--- a/results/by_outcome/full_results_education_PGI_Sisters_MI.xlsx
+++ b/results/by_outcome/full_results_education_PGI_Sisters_MI.xlsx
@@ -486,10 +486,10 @@
         <v>#NUM!</v>
       </c>
       <c r="H2" t="n">
-        <v>0.568336485682984</v>
+        <v>0.563574654557566</v>
       </c>
       <c r="I2" t="n">
-        <v>0.330070066857121</v>
+        <v>0.32793797668125</v>
       </c>
       <c r="J2" t="e">
         <v>#NUM!</v>
@@ -507,7 +507,7 @@
         <v>#NUM!</v>
       </c>
       <c r="O2" t="n">
-        <v>0.431864501715099</v>
+        <v>0.436624757365724</v>
       </c>
     </row>
     <row r="3">
@@ -527,10 +527,10 @@
         <v>#NUM!</v>
       </c>
       <c r="F3" t="n">
-        <v>0.569541729316187</v>
+        <v>0.568610238668928</v>
       </c>
       <c r="G3" t="n">
-        <v>0.364407141095672</v>
+        <v>0.356845174825524</v>
       </c>
       <c r="H3" t="e">
         <v>#NUM!</v>
@@ -565,13 +565,13 @@
         <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>0.604017668620019</v>
+        <v>0.604096999436549</v>
       </c>
       <c r="D4" t="n">
-        <v>0.396336098359715</v>
+        <v>0.396256960283055</v>
       </c>
       <c r="E4" t="n">
-        <v>1.00035376697973</v>
+        <v>1.0003539597196</v>
       </c>
       <c r="F4" t="e">
         <v>#NUM!</v>
@@ -586,19 +586,19 @@
         <v>#NUM!</v>
       </c>
       <c r="J4" t="n">
-        <v>0.396195937348151</v>
+        <v>0.396116750876159</v>
       </c>
       <c r="K4" t="n">
-        <v>0.364278271350985</v>
+        <v>0.356718910678852</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00120481729895002</v>
+        <v>0.00503380208141534</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0356685643669483</v>
+        <v>0.0405080064895659</v>
       </c>
       <c r="N4" t="n">
-        <v>0.365483088649935</v>
+        <v>0.361752712760268</v>
       </c>
       <c r="O4" t="e">
         <v>#NUM!</v>
@@ -643,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>0.396195937348151</v>
+        <v>0.396116750876159</v>
       </c>
       <c r="D2" t="n">
-        <v>0.338240775414672</v>
+        <v>0.337392676992676</v>
       </c>
       <c r="E2" t="n">
-        <v>0.454151099281629</v>
+        <v>0.454840824759641</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0000000000000000000000000000000000000000614466827983977</v>
+        <v>0.000000000000000000000000000000000000000666233437787049</v>
       </c>
     </row>
     <row r="3">
@@ -663,16 +663,16 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.365483088649935</v>
+        <v>0.361752712760268</v>
       </c>
       <c r="D3" t="n">
-        <v>0.300622936335278</v>
+        <v>0.302270105500851</v>
       </c>
       <c r="E3" t="n">
-        <v>0.430343240964591</v>
+        <v>0.421235320019684</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000000000000000000000000000234380950335795</v>
+        <v>0.00000000000000000000000000000000944918558150938</v>
       </c>
     </row>
     <row r="4">
@@ -683,16 +683,16 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.431864501715099</v>
+        <v>0.436624757365724</v>
       </c>
       <c r="D4" t="n">
-        <v>0.36805376589927</v>
+        <v>0.377687953754804</v>
       </c>
       <c r="E4" t="n">
-        <v>0.495675237530928</v>
+        <v>0.495561560976645</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000000000000000000000000000000000000000372385131415106</v>
+        <v>0.00000000000000000000000000000000000000000000000931601266467244</v>
       </c>
     </row>
     <row r="5">
@@ -703,16 +703,16 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0663814130651642</v>
+        <v>0.0748720446054569</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0347756612825908</v>
+        <v>0.0470738567571134</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0979871648477377</v>
+        <v>0.1026702324538</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0000384664019012518</v>
+        <v>0.000000129897682723279</v>
       </c>
     </row>
   </sheetData>
